--- a/raw-xlsx/66Khargram_2026_Form20.xlsx
+++ b/raw-xlsx/66Khargram_2026_Form20.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>GP Name</t>
+          <t>GP</t>
         </is>
       </c>
     </row>
